--- a/Docs/params_catalog/SPOD_PARAMS_CATALOG_LEAF_v3.xlsx
+++ b/Docs/params_catalog/SPOD_PARAMS_CATALOG_LEAF_v3.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Бизнес-статус конкурса (например АКТИВНЫЙ).</t>
+          <t>Бизнес-статус конкурса: АКТИВНЫЙ | АРХИВНЫЙ.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Тип расчёта (код).</t>
+          <t>Тип расчёта: 0 | 1. (не используется) 0 — промышленный / 1 — ручной.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Текстовое описание конкурса для пользователя/админки.</t>
+          <t>Текст описания для конкурса/турнира (на странице Детальная карточка турнира).</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Метод фактора (FACT и др.).</t>
+          <t>FACT | FACT0-FACT1 | FACT0-RUN_RATE1_DOWN | RUN_RATE — для автоматических турниров способ расчета на данных источников.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>**Смысл (гипотеза):** точность / шаг отображения или расчёта (уточняется в ТЗ СПОД). **Тип JSON:** целое число. **CONTEST_TYPE:** все три типа. **Домен в выборке:** ТУРНИРНЫЙ — `0`, `1`, `2`, `3`, `5`; накопительный и индивидуальный — `0`, `2`.</t>
+          <t>**Смысл (гипотеза):** число знаков после запятой для отображения. **Тип JSON:** целое число. **CONTEST_TYPE:** все три типа. **Домен в выборке:** ТУРНИРНЫЙ — `0`, `1`, `2`, `3`, `5`; накопительный и индивидуальный — `0`, `2`.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>**Тип:** строка. **CONTEST_TYPE:** все. **Домен:** **`""`**, **`MILLIONS`**, **`THOUSANDS`** (у **ИНДИВИДУАЛЬНЫЙ** в выборке только **`""`**).</t>
+          <t>**Смысл (гипотеза):** уменьшение отображаемого показателя до млн / до тыс. **Тип:** строка. **CONTEST_TYPE:** все. **Домен:** **`""`**, **`MILLIONS`**, **`THOUSANDS`** (у **ИНДИВИДУАЛЬНЫЙ** в выборке только **`""`**).</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>**Тип:** массив строк. **REWARD_TYPE:** все типы. **Длина:** BADGE 0–5 элементов; ITEM 0–6; LABEL 0–1; CRYSTAL в выборке всегда пустой массив. **Элементы:** в BADGE/ITEM — в основном **длинные текстовые описания** (подсказки/условия); в LABEL — короткие фразы про метку; в CRYSTAL — нет заполненных элементов в выборке.</t>
+          <t>**Смысл (гипотеза):** тексты особенностей: для турнира — в детальной карточке; для награды — показываем в Награде. **Тип:** массив строк. **REWARD_TYPE:** все типы. **Длина:** BADGE 0–5 элементов; ITEM 0–6; LABEL 0–1; CRYSTAL в выборке всегда пустой массив. **Элементы:** в BADGE/ITEM — в основном **длинные текстовые описания** (подсказки/условия); в LABEL — короткие фразы про метку; в CRYSTAL — нет заполненных элементов в выборке.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>**Тип:** целое число. **CONTEST_TYPE:** все. **Домен:** турнир — `0`…`3`; накопительный и индивидуальный — в выборке **`1`**.</t>
+          <t>**Смысл (гипотеза):** мин. число участников чтобы считать победителей (исключаем соревнование сам с собой); обычно `1` | `2` | `3`. **Тип:** целое число. **CONTEST_TYPE:** все. **Домен:** турнир — `0`…`3`; накопительный и индивидуальный — в выборке **`1`**.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>**Тип:** строка (момент начисления награды). **CONTEST_TYPE:** все. **Домен:** **`AFTER`** (после); **`DURIN`** — только у накопительного и индивидуального (см. примечание про опечатку). У **ТУРНИРНЫЙ** в выборке только **`AFTER`**.</t>
+          <t>**Смысл (гипотеза):** момент награждения — после закрытия / во время турнира. **Тип:** строка (момент начисления награды). **CONTEST_TYPE:** все. **Домен:** **`AFTER`** (после закрытия турнира); **`DURIN`** — во время турнира (см. примечание про опечатку). У **ТУРНИРНЫЙ** в выборке только **`AFTER`**.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>**Тип:** массив; в выборке **всегда пустой**. **CONTEST_TYPE:** все.</t>
+          <t>**Смысл (гипотеза):** если указаны табельные — эти сотрудники НЕ увидят турнир. **Тип:** массив; в выборке **всегда пустой**. **CONTEST_TYPE:** все.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>**Тип:** массив строк. **REWARD_TYPE:** BADGE; редко (9 строк); элементы — **длинный текст** (до ~127 символов).</t>
+          <t>**Смысл (гипотеза):** преференции, если предусмотрены за награду. **Тип:** массив строк. **REWARD_TYPE:** BADGE; редко (9 строк); элементы — **длинный текст** (до ~127 символов).</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>**Тип:** строка. **CONTEST_TYPE:** все. **Домен:** **`all`**, **`one`** (все победители / один).</t>
+          <t>**Смысл (гипотеза):** вручаем одну из 3 наград или все. **Тип:** строка. **CONTEST_TYPE:** все. **Домен:** **`all`**, **`one`** (все победители / один).</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Метод расчёта по индикатору (INTEGRAL и др.).</t>
+          <t>INTEGRAL | RELATION. Метод расчета показателя.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Период конкурса: строка или JSON-объект с period_code / датами.</t>
+          <t>Периоды через ; или пусто → []. Обычно пусто.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Предмет конкурса (EMPLOYEE и др.).</t>
+          <t>Предмет конкурса. Обычно: EMPLOYEE. Кто участник.</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Тип конкурса (ТУРНИРНЫЙ / ИНДИВИДУАЛЬНЫЙ / …); влияет на схему CONTEST_FEATURE.</t>
+          <t>ТУРНИРНЫЙ (до 3 BADGE) | ИНДИВИДУАЛЬНЫЙ | ИНДИВИДУАЛЬНЫЙ НАКОПИТЕЛЬНЫЙ (1 BADGE); влияет на схему CONTEST_FEATURE.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Дата начала действия записи конкурса (YYYY-MM-DD).</t>
+          <t>Дата начала YYYY-MM-DD. Часто начало года.</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Тип отметки фактора (CRITERION и др.).</t>
+          <t>CRITERION | RATING_MAX | RATING_MIN — способ выбора победителей (достиг показателя / больше других / меньше других).</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Правило сопоставления фактора (= и др.).</t>
+          <t>Сравнение фактора: = | &gt; | &gt;=.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Постобработка факта (коды/флаги).</t>
+          <t>Правило постобработки показателя конкурса; часто пусто. PERCENTILE — перцентиль от фактического показателя.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Отображаемое наименование конкурса/турнира.</t>
+          <t>Отображаемое название конкурса/турнира (на странице Турниры/Детальная карточка).</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Код метода планирования (FACT, PRESET_VALUE и др.).</t>
+          <t>DEPENDS_PREVIOUS_PERIOD | PRESET_VALUE — метод расчета планового показателя (из прошлого периода / фиксированное значение).</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Модификатор метода плана (имя с опечаткой Metod).</t>
+          <t>Модификатор плана. Обычно: MULTIPLIER.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Значение модификатора плана.</t>
+          <t>Значение планового показателя (0, 1, 1000, …).</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Продукт / тематика конкурса.</t>
+          <t>Продукт / тематика конкурса (свободный текст).</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Группа продукта в классификаторе.</t>
+          <t>Группа продукта из классификатора (можно будет в дальнейшем дополнить).</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Единица/подпись отображения индикатора (шт., Факт и т.п.).</t>
+          <t>Единица/подпись индикатора: шт. | Факт | % | … на списке показателей подпись к единицам данных.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Периодичность обновления источника данных.</t>
+          <t>Частота обновления источника: 1 | 7 | 10 (дни). (не используется)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Тип целевой аудитории (числовой/строковый код).</t>
+          <t>Среда конкурса: ПРОМ | ТЕСТ.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Краткое отображаемое название награды.</t>
+          <t>Краткое название бейджа / отображаемое название награды.</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -19726,7 +19726,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>**Тип:** массив строк. **REWARD_TYPE:** все типы. **Длина:** BADGE 0–5 элементов; ITEM 0–6; LABEL 0–1; CRYSTAL в выборке всегда пустой массив. **Элементы:** в BADGE/ITEM — в основном **длинные текстовые описания** (подсказки/условия); в LABEL — короткие фразы про метку; в CRYSTAL — нет заполненных элементов в выборке.</t>
+          <t>**Смысл (гипотеза):** тексты особенностей: для турнира — в детальной карточке; для награды — показываем в Награде. **Тип:** массив строк. **REWARD_TYPE:** все типы. **Длина:** BADGE 0–5 элементов; ITEM 0–6; LABEL 0–1; CRYSTAL в выборке всегда пустой массив. **Элементы:** в BADGE/ITEM — в основном **длинные текстовые описания** (подсказки/условия); в LABEL — короткие фразы про метку; в CRYSTAL — нет заполненных элементов в выборке.</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -23827,7 +23827,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>**Тип:** строка **`Y` / `N`**. **REWARD_TYPE:** BADGE; во всех строках типа.</t>
+          <t>**Смысл (гипотеза):** мастер-бейдж: **Y** — для награды / **N** — для турнира. **Тип:** строка **`Y` / `N`**. **REWARD_TYPE:** BADGE; во всех строках типа.</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -23991,7 +23991,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>**Тип:** строка. **REWARD_TYPE:** BADGE; не во всех строках. **Значения в выборке:** **`AIPROMPT`**, **`TEMPLATE`**.</t>
+          <t>**Смысл (гипотеза):** тип новости — генерит ИИ (`AIPROMPT`) / по шаблону (`TEMPLATE`). **Тип:** строка. **REWARD_TYPE:** BADGE; не во всех строках. **Значения в выборке:** **`AIPROMPT`**, **`TEMPLATE`**.</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -24807,7 +24807,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>**Тип:** массив строк. **REWARD_TYPE:** BADGE; редко (9 строк); элементы — **длинный текст** (до ~127 символов).</t>
+          <t>**Смысл (гипотеза):** преференции, если предусмотрены за награду. **Тип:** массив строк. **REWARD_TYPE:** BADGE; редко (9 строк); элементы — **длинный текст** (до ~127 символов).</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>**Тип:** строка. **REWARD_TYPE:** BADGE; 37 строк. **Домен:** **длинный текст** (критерий победы в турнире).</t>
+          <t>**Смысл (гипотеза):** текст критерия победы для ИИ создания новости. **Тип:** строка. **REWARD_TYPE:** BADGE; 37 строк. **Домен:** **длинный текст** (критерий победы в турнире).</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -27256,7 +27256,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>Класс/код условия начисления.</t>
+          <t>Класс/код условия начисления (часто пусто или код).</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
@@ -27406,7 +27406,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Стоимость награды в условных единицах.</t>
+          <t>Стоимость в кристаллах (часто 0…14).</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -27559,7 +27559,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Полное описание / условия для пользователя.</t>
+          <t>Полное описание награды.</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
@@ -28934,7 +28934,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>Дата окончания периода.</t>
+          <t>Дата окончания турнира.</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
@@ -30644,7 +30644,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Дата фиксации/публикации результата.</t>
+          <t>Дата подведения итогов турнира.</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
@@ -30797,7 +30797,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Дата начала периода.</t>
+          <t>Дата старта турнира.</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
@@ -35707,7 +35707,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07 23:46:27</t>
+          <t>2026-08-14 23:07:37</t>
         </is>
       </c>
     </row>
